--- a/knowledge/问题清单.xlsx
+++ b/knowledge/问题清单.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\QUANZHAN\PROJECT\ai-learning\knowledge\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF6D6AC7-735F-401C-8E42-34546DD26037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32B486AA-A33A-459E-BF4A-8A96EAFD9E48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="28">
   <si>
     <t>问题</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -66,9 +66,6 @@
   <si>
     <t>林冲的结局？</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>答错</t>
   </si>
   <si>
     <t>根据提供的资料，没有关于林冲结局的记载。资料1只提到他一生分为四个阶段，资料2和资料3也只讲到第一次忍让和刺配沧州为止，均未提及最终结局。
@@ -142,6 +139,15 @@
   </si>
   <si>
     <t>林冲的家庭背景是什么？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>林冲的父亲是东京的提辖官，岳父张教头也曾是禁军教头，家境殷实。妻子张氏贤惠，两人感情深厚，膝下无子。“操刀鬼”曹正是他的徒弟。
+用了【资料1】</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026/10/4修改后通过</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -186,13 +192,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -537,6 +543,7 @@
     <col min="3" max="3" width="5.625" customWidth="1"/>
     <col min="4" max="4" width="6.25" customWidth="1"/>
     <col min="5" max="6" width="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -551,7 +558,7 @@
       </c>
       <c r="D1" s="4"/>
       <c r="E1" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F1" s="7" t="s">
         <v>2</v>
@@ -569,17 +576,17 @@
         <v>3</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
+      <c r="F2" s="6"/>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="6" t="s">
@@ -589,10 +596,14 @@
         <v>6</v>
       </c>
       <c r="E3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
     </row>
     <row r="4" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
@@ -608,41 +619,43 @@
         <v>8</v>
       </c>
       <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
+      <c r="F4" s="6"/>
       <c r="G4" s="5"/>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="9" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>11</v>
-      </c>
       <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="5" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="6" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>13</v>
-      </c>
       <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
+      <c r="F6" s="6"/>
       <c r="G6" s="5"/>
     </row>
     <row r="7" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -650,16 +663,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>15</v>
-      </c>
       <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
+      <c r="F7" s="6"/>
       <c r="G7" s="5"/>
     </row>
     <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -667,50 +680,52 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>17</v>
-      </c>
       <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
+      <c r="F8" s="6"/>
       <c r="G8" s="5"/>
     </row>
     <row r="9" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>19</v>
-      </c>
       <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="5" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="10" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>21</v>
-      </c>
       <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
+      <c r="F10" s="6"/>
       <c r="G10" s="5"/>
     </row>
     <row r="11" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -718,22 +733,22 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>23</v>
-      </c>
       <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
+      <c r="F11" s="6"/>
       <c r="G11" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C11 F2:F11" xr:uid="{43A0350C-04EF-4545-AD59-0D697F96AA1E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F11 C2:C11" xr:uid="{43A0350C-04EF-4545-AD59-0D697F96AA1E}">
       <formula1>"答对,答错,胡编"</formula1>
     </dataValidation>
   </dataValidations>
